--- a/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
+++ b/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="B1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.85546875" customWidth="1" min="1" max="1"/>
@@ -571,7 +571,7 @@
         <v>2010</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         <v>2050</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
+++ b/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.85546875" customWidth="1" min="1" max="1"/>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2010</v>
+        <v>2025</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         <v>2050</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -607,29 +607,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>FLO_SUB</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ELC_FIN_DEM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ELC_GRID_RES</t>
-        </is>
-      </c>
-    </row>
+    <row r="5"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
